--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,57 +1146,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136494585</v>
+        <v>136619080</v>
       </c>
       <c r="B6" t="n">
-        <v>56935</v>
+        <v>58165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208255</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kulle med stenblock, Djurholmamossen, Sk</t>
+          <t>N Rösjön Västersjön, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380073</v>
+        <v>380167</v>
       </c>
       <c r="R6" t="n">
-        <v>6246782</v>
+        <v>6246658</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,49 +1219,54 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494585</t>
+          <t>https://artportalen.se/Sighting/136619080</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136494463</v>
+        <v>136494585</v>
       </c>
       <c r="B7" t="n">
-        <v>98204</v>
+        <v>56935</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,38 +1274,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>208255</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
+          <t>Kulle med stenblock, Djurholmamossen, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380239</v>
+        <v>380073</v>
       </c>
       <c r="R7" t="n">
-        <v>6246730</v>
+        <v>6246782</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1367,13 +1373,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494463</t>
+          <t>https://artportalen.se/Sighting/136494585</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136494826</v>
+        <v>136494463</v>
       </c>
       <c r="B8" t="n">
         <v>98204</v>
@@ -1408,17 +1414,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bokbacke, Djurholmamossen, Sk</t>
+          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379956</v>
+        <v>380239</v>
       </c>
       <c r="R8" t="n">
-        <v>6246688</v>
+        <v>6246730</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,7 +1484,342 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136494463</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136494826</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bokbacke, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>379956</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6246688</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136494826</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136619078</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N Rösjön Västersjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>380268</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6246709</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136619078</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136619082</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N Rösjön Västersjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>379968</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6246688</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136619082</t>
         </is>
       </c>
     </row>
@@ -1491,6 +1832,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136494442</v>
       </c>
       <c r="B4" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136494475</v>
       </c>
       <c r="B5" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136619080</v>
       </c>
       <c r="B6" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136494585</v>
       </c>
       <c r="B7" t="n">
-        <v>56935</v>
+        <v>56937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136494463</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>136494826</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>136619078</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>136619082</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,60 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74197490</v>
+        <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>57813</v>
+        <v>96957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100136</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djurholmen, Sk</t>
+          <t>Hallandsåsen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380056</v>
+        <v>380064</v>
       </c>
       <c r="R3" t="n">
-        <v>6246788</v>
+        <v>6246780</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sedd av Wanja Zeilon och Fredrik Broberg.</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,49 +886,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Jesper Hansson</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74197490</t>
+          <t>https://artportalen.se/Sighting/137150235</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136494442</v>
+        <v>74197490</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>57813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100136</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,23 +940,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hässlebo våt sänka, Djurholmamossen, Sk</t>
+          <t>Djurholmen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380119</v>
+        <v>380056</v>
       </c>
       <c r="R4" t="n">
-        <v>6246628</v>
+        <v>6246788</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,12 +980,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2018-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sedd av Wanja Zeilon och Fredrik Broberg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,28 +1005,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Via Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494442</t>
+          <t>https://artportalen.se/Sighting/74197490</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136494475</v>
+        <v>136494442</v>
       </c>
       <c r="B5" t="n">
         <v>58167</v>
@@ -1071,14 +1065,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
+          <t>Hässlebo våt sänka, Djurholmamossen, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380239</v>
+        <v>380119</v>
       </c>
       <c r="R5" t="n">
-        <v>6246730</v>
+        <v>6246628</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1140,13 +1134,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494475</t>
+          <t>https://artportalen.se/Sighting/136494442</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136619080</v>
+        <v>136494475</v>
       </c>
       <c r="B6" t="n">
         <v>58167</v>
@@ -1174,25 +1168,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Rösjön Västersjön, Sk</t>
+          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380167</v>
+        <v>380239</v>
       </c>
       <c r="R6" t="n">
-        <v>6246658</v>
+        <v>6246730</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,19 +1220,9 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,74 +1237,74 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136619080</t>
+          <t>https://artportalen.se/Sighting/136494475</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136494585</v>
+        <v>136619080</v>
       </c>
       <c r="B7" t="n">
-        <v>56937</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208255</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kulle med stenblock, Djurholmamossen, Sk</t>
+          <t>N Rösjön Västersjön, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380073</v>
+        <v>380167</v>
       </c>
       <c r="R7" t="n">
-        <v>6246782</v>
+        <v>6246658</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,91 +1331,92 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494585</t>
+          <t>https://artportalen.se/Sighting/136619080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136494463</v>
+        <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>98230</v>
+        <v>58167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
+          <t>Hallandsåsen, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380239</v>
+        <v>380274</v>
       </c>
       <c r="R8" t="n">
-        <v>6246730</v>
+        <v>6246709</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,18 +1443,27 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1477,65 +1478,57 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494463</t>
+          <t>https://artportalen.se/Sighting/137150223</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136494826</v>
+        <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>98230</v>
+        <v>58167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bokbacke, Djurholmamossen, Sk</t>
+          <t>Hallandsåsen, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>379956</v>
+        <v>380169</v>
       </c>
       <c r="R9" t="n">
-        <v>6246688</v>
+        <v>6246659</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,18 +1555,27 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1588,23 +1590,19 @@
           <t>Petra Borgcrantz</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136494826</t>
+          <t>https://artportalen.se/Sighting/137150224</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136619078</v>
+        <v>136494585</v>
       </c>
       <c r="B10" t="n">
-        <v>98230</v>
+        <v>56937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,37 +1610,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>208255</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Rösjön Västersjön, Sk</t>
+          <t>Kulle med stenblock, Djurholmamossen, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380268</v>
+        <v>380073</v>
       </c>
       <c r="R10" t="n">
-        <v>6246709</v>
+        <v>6246782</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,54 +1676,49 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136619078</t>
+          <t>https://artportalen.se/Sighting/136494585</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136619082</v>
+        <v>137150234</v>
       </c>
       <c r="B11" t="n">
-        <v>98230</v>
+        <v>56937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,37 +1726,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>208255</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Rösjön Västersjön, Sk</t>
+          <t>Hallandsåsen, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>379968</v>
+        <v>380058</v>
       </c>
       <c r="R11" t="n">
-        <v>6246688</v>
+        <v>6246781</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,18 +1814,688 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137150234</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136494463</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>380239</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6246730</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494463</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136494826</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bokbacke, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>379956</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6246688</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494826</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136619078</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N Rösjön Västersjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>380268</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6246709</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136619078</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136619082</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N Rösjön Västersjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>379968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6246688</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136619082</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137150222</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hallandsåsen, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>380266</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6246702</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150222</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137150230</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98234</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hallandsåsen, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>379967</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6246693</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150230</t>
         </is>
       </c>
     </row>
@@ -1835,6 +2511,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>136619078</v>
       </c>
       <c r="B14" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>136619082</v>
       </c>
       <c r="B15" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>136619078</v>
       </c>
       <c r="B14" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>136619082</v>
       </c>
       <c r="B15" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136619080</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>137150234</v>
       </c>
       <c r="B11" t="n">
-        <v>56937</v>
+        <v>56950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>136619078</v>
       </c>
       <c r="B14" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>136619082</v>
       </c>
       <c r="B15" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>136619080</v>
       </c>
       <c r="B7" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>137150234</v>
       </c>
       <c r="B11" t="n">
-        <v>56950</v>
+        <v>56952</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>136619078</v>
       </c>
       <c r="B14" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>136619082</v>
       </c>
       <c r="B15" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>137150234</v>
       </c>
       <c r="B11" t="n">
-        <v>56952</v>
+        <v>56962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>137150234</v>
       </c>
       <c r="B11" t="n">
-        <v>56962</v>
+        <v>56963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137150235</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137150223</v>
       </c>
       <c r="B8" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137150224</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>137150234</v>
       </c>
       <c r="B11" t="n">
-        <v>56963</v>
+        <v>56966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>137150222</v>
       </c>
       <c r="B16" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137150230</v>
       </c>
       <c r="B17" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
